--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\balaj\OneDrive\Desktop\DSA\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_21AE599A8FA94657D6F20759884190C70E00C015" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="394">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -40,16 +34,16 @@
     <t>Link 3</t>
   </si>
   <si>
-    <t>1. Pattern: Two Pointers</t>
-  </si>
-  <si>
-    <t>Pair with Target Sum (easy)</t>
+    <t xml:space="preserve">1. Pattern: Two Pointers                       </t>
+  </si>
+  <si>
+    <t>Pair with Target Sum (easy)                   -- Done</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/two-sum-ii-input-array-is-sorted/description/</t>
   </si>
   <si>
-    <t>Rearrange 0 and 1</t>
+    <t>Rearrange 0 and 1                                --Done</t>
   </si>
   <si>
     <t>https://www.geeksforgeeks.org/problems/segregate-0s-and-1s5106/1</t>
@@ -59,11 +53,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/remove-duplicates-from-sorted-list/</t>
     </r>
@@ -73,11 +72,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/remove-duplicates-from-sorted-array-ii/</t>
     </r>
@@ -93,11 +97,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/3sum/</t>
     </r>
@@ -107,11 +116,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/3sum-closest/</t>
     </r>
@@ -127,11 +141,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/subarray-product-less-than-k/</t>
     </r>
@@ -147,11 +166,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/4sum/</t>
     </r>
@@ -161,11 +185,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/backspace-string-compare/</t>
     </r>
@@ -175,22 +204,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/shortest-unsorted-continuous-subarray/</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.ideserve.co.in/learn/minimum-length-subarray-sorting-which-results-in-sorted-array</t>
     </r>
@@ -203,11 +242,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/linked-list-cycle/</t>
     </r>
@@ -217,11 +261,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/linked-list-cycle-ii/</t>
     </r>
@@ -231,11 +280,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/happy-number/</t>
     </r>
@@ -251,11 +305,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/middle-of-the-linked-list/</t>
     </r>
@@ -265,11 +324,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/palindrome-linked-list/</t>
     </r>
@@ -279,11 +343,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/reorder-list/</t>
     </r>
@@ -293,11 +362,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/circular-array-loop/</t>
     </r>
@@ -328,11 +402,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/fruit-into-baskets/</t>
     </r>
@@ -342,11 +421,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/longest-substring-without-repeating-characters/</t>
     </r>
@@ -356,11 +440,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/longest-repeating-character-replacement/</t>
     </r>
@@ -370,11 +459,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/max-consecutive-ones-iii/</t>
     </r>
@@ -393,11 +487,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/permutation-in-string/</t>
     </r>
@@ -407,11 +506,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/find-all-anagrams-in-a-string/</t>
     </r>
@@ -526,11 +630,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/check-if-any-two-intervals-overlap-among-a-given-set-of-intervals/</t>
     </r>
@@ -546,11 +655,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/maximum-cpu-load-from-the-given-list-of-jobs/</t>
     </r>
@@ -560,11 +674,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.codertrain.co/employee-free-time</t>
     </r>
@@ -577,11 +696,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/sort-an-array-which-contain-1-to-n-values-in-on-using-cycle-sort/</t>
     </r>
@@ -591,11 +715,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/missing-number/</t>
     </r>
@@ -605,11 +734,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/find-all-numbers-disappeared-in-an-array/</t>
     </r>
@@ -619,11 +753,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/find-the-duplicate-number/</t>
     </r>
@@ -633,11 +772,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/find-all-duplicates-in-an-array/</t>
     </r>
@@ -647,11 +791,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://thecodingsimplified.com/find-currupt-pair/</t>
     </r>
@@ -661,11 +810,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/first-missing-positive/</t>
     </r>
@@ -675,11 +829,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://thecodingsimplified.com/find-the-first-k-missing-positive-number/</t>
     </r>
@@ -692,11 +851,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/reverse-linked-list/</t>
     </r>
@@ -706,11 +870,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/reverse-linked-list-ii/</t>
     </r>
@@ -720,11 +889,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/reverse-nodes-in-k-group/</t>
     </r>
@@ -734,11 +908,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/reverse-alternate-k-nodes-in-a-singly-linked-list/</t>
     </r>
@@ -748,11 +927,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/rotate-list/</t>
     </r>
@@ -771,11 +955,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/valid-parentheses/description/</t>
     </r>
@@ -794,11 +983,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/daily-temperatures/</t>
     </r>
@@ -808,11 +1002,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/remove-nodes-from-linked-list/</t>
     </r>
@@ -822,11 +1021,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/remove-all-adjacent-duplicates-in-string-ii/</t>
     </r>
@@ -842,11 +1046,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/remove-k-digits/</t>
     </r>
@@ -859,11 +1068,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/first-unique-character-in-a-string/</t>
     </r>
@@ -873,11 +1087,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/largest-unique-number/</t>
     </r>
@@ -887,11 +1106,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/maximum-number-of-balloons/</t>
     </r>
@@ -901,11 +1125,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/longest-palindrome/</t>
     </r>
@@ -915,11 +1144,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/ransom-note/</t>
     </r>
@@ -932,11 +1166,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/binary-tree-level-order-traversal/</t>
     </r>
@@ -946,11 +1185,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/binary-tree-level-order-traversal-ii/</t>
     </r>
@@ -960,11 +1204,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/binary-tree-zigzag-level-order-traversal/</t>
     </r>
@@ -974,11 +1223,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/average-of-levels-in-binary-tree/</t>
     </r>
@@ -988,11 +1242,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/minimum-depth-of-binary-tree/</t>
     </r>
@@ -1002,11 +1261,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/maximum-depth-of-binary-tree/</t>
     </r>
@@ -1016,11 +1280,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/level-order-successor-of-a-node-in-binary-tree/</t>
     </r>
@@ -1030,11 +1299,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/populating-next-right-pointers-in-each-node/</t>
     </r>
@@ -1044,11 +1318,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.educative.io/m/connect-all-siblings</t>
     </r>
@@ -1058,11 +1337,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/binary-tree-right-side-view/</t>
     </r>
@@ -1075,11 +1359,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/path-sum/</t>
     </r>
@@ -1089,11 +1378,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/path-sum-iii/</t>
     </r>
@@ -1103,11 +1397,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/sum-root-to-leaf-numbers/</t>
     </r>
@@ -1117,11 +1416,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/check-root-leaf-path-given-sequence/</t>
     </r>
@@ -1130,26 +1434,20 @@
     <t>Count Paths for a Sum (medium)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-      </rPr>
-      <t>https://leetcode.com/problems/path-sum-iii/</t>
-    </r>
-  </si>
-  <si>
     <t>Problem Challenge 1: Tree Diameter (medium)</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/diameter-of-binary-tree/</t>
     </r>
@@ -1159,11 +1457,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/binary-tree-maximum-path-sum/</t>
     </r>
@@ -1182,11 +1485,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/find-if-path-exists-in-graph/</t>
     </r>
@@ -1196,11 +1504,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/number-of-provinces/</t>
     </r>
@@ -1210,11 +1523,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/minimum-number-of-vertices-to-reach-all-nodes/</t>
     </r>
@@ -1227,11 +1545,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/number-of-islands/</t>
     </r>
@@ -1244,11 +1567,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/flood-fill/</t>
     </r>
@@ -1258,11 +1586,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/number-of-closed-islands/</t>
     </r>
@@ -1284,11 +1617,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/find-median-from-data-stream/</t>
     </r>
@@ -1298,11 +1636,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/sliding-window-median/</t>
     </r>
@@ -1312,11 +1655,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/ipo/</t>
     </r>
@@ -1326,11 +1674,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.interviewbit.com/problems/maximum-sum-combinations/</t>
     </r>
@@ -1343,11 +1696,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.educative.io/courses/grokking-the-coding-interview/gx2OqlvEnWG</t>
     </r>
@@ -1357,11 +1715,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.educative.io/courses/grokking-the-coding-interview/7npk3V3JQNr</t>
     </r>
@@ -1371,11 +1734,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.educative.io/courses/grokking-the-coding-interview/B8R83jyN3KY</t>
     </r>
@@ -1391,11 +1759,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/generalized-abbreviation/</t>
     </r>
@@ -1408,11 +1781,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/order-agnostic-binary-search/</t>
     </r>
@@ -1422,22 +1800,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/ceiling-in-a-sorted-array/</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/floor-in-a-sorted-array/</t>
     </r>
@@ -1447,11 +1835,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/find-smallest-letter-greater-than-target/</t>
     </r>
@@ -1461,11 +1854,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/find-first-and-last-position-of-element-in-sorted-array/</t>
     </r>
@@ -1475,11 +1873,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/find-position-element-sorted-array-infinite-numbers/</t>
     </r>
@@ -1492,11 +1895,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/find-the-maximum-element-in-an-array-which-is-first-increasing-and-then-decreasing/</t>
     </r>
@@ -1506,11 +1914,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/find-in-mountain-array/</t>
     </r>
@@ -1520,11 +1933,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/search-in-rotated-sorted-array/</t>
     </r>
@@ -1534,11 +1952,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/find-rotation-count-rotated-sorted-array/</t>
     </r>
@@ -1548,11 +1971,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/search-a-2d-matrix/</t>
     </r>
@@ -1562,11 +1990,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/minimum-number-of-days-to-make-m-bouquets/</t>
     </r>
@@ -1576,11 +2009,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/koko-eating-bananas/</t>
     </r>
@@ -1590,11 +2028,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/capacity-to-ship-packages-within-d-days/</t>
     </r>
@@ -1604,11 +2047,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/median-of-two-sorted-arrays/</t>
     </r>
@@ -1636,11 +2084,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://github.com/dipjul/Grokking-the-Coding-Interview-Patterns-for-Coding-Questions/blob/master/13.-pattern-top-k-elements/02.top-k-numbers.md</t>
     </r>
@@ -1653,11 +2106,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/k-closest-points-to-origin/</t>
     </r>
@@ -1676,11 +2134,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/kth-largest-element-in-a-stream/</t>
     </r>
@@ -1711,11 +2174,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://github.com/dipjul/Grokking-the-Coding-Interview-Patterns-for-Coding-Questions/blob/master/13.-pattern-top-k-elements/13.HeapImplementation.md</t>
     </r>
@@ -1728,11 +2196,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/merge-k-sorted-lists/</t>
     </r>
@@ -1742,11 +2215,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/find-m-th-smallest-value-in-k-sorted-arrays/</t>
     </r>
@@ -1756,11 +2234,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.educative.io/courses/grokking-the-coding-interview/x1NJVYKNvqz</t>
     </r>
@@ -1770,11 +2253,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/smallest-range-covering-elements-from-k-lists/</t>
     </r>
@@ -1790,11 +2278,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/valid-palindrome-ii/</t>
     </r>
@@ -1804,11 +2297,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/maximum-length-of-pair-chain/</t>
     </r>
@@ -1818,11 +2316,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/minimum-add-to-make-parentheses-valid/</t>
     </r>
@@ -1832,11 +2335,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/remove-duplicate-letters/</t>
     </r>
@@ -1846,11 +2354,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/largest-palindromic-number/</t>
     </r>
@@ -1860,11 +2373,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/removing-minimum-and-maximum-from-array/</t>
     </r>
@@ -1877,11 +2395,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/0-1-knapsack-problem-dp-10/</t>
     </r>
@@ -1891,11 +2414,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/partition-equal-subset-sum/</t>
     </r>
@@ -1905,11 +2433,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/subset-sum-problem-dp-25/</t>
     </r>
@@ -1919,11 +2452,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/partition-a-set-into-two-subsets-such-that-the-difference-of-subset-sums-is-minimum/</t>
     </r>
@@ -1942,33 +2480,48 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/combination-sum/</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/combination-sum-ii/</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/combination-sum-iii/</t>
     </r>
@@ -1978,22 +2531,32 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/word-search/</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/word-search-ii/</t>
     </r>
@@ -2003,11 +2566,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/sudoku-solver/</t>
     </r>
@@ -2017,11 +2585,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/factor-combinations/</t>
     </r>
@@ -2031,11 +2604,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/split-a-string-into-the-max-number-of-unique-substrings/</t>
     </r>
@@ -2048,11 +2626,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/implement-trie-prefix-tree/</t>
     </r>
@@ -2062,11 +2645,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/index-pairs-of-a-string/</t>
     </r>
@@ -2076,11 +2664,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/design-add-and-search-words-data-structure/</t>
     </r>
@@ -2090,11 +2683,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/extra-characters-in-a-string/</t>
     </r>
@@ -2104,11 +2702,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/search-suggestions-system/</t>
     </r>
@@ -2121,11 +2724,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://www.youtube.com/watch?v=cIBFEhD77b4</t>
     </r>
@@ -2135,11 +2743,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/course-schedule/</t>
     </r>
@@ -2148,26 +2761,20 @@
     <t>Tasks Scheduling Order (medium)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-      </rPr>
-      <t>https://leetcode.com/problems/course-schedule/</t>
-    </r>
-  </si>
-  <si>
     <t>All Tasks Scheduling Orders (hard)</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/course-schedule-ii/</t>
     </r>
@@ -2177,11 +2784,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/alien-dictionary/</t>
     </r>
@@ -2191,11 +2803,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/sequence-reconstruction/</t>
     </r>
@@ -2205,11 +2822,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/minimum-height-trees/</t>
     </r>
@@ -2222,47 +2844,51 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/redundant-connection/</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/redundant-connection-ii/</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-      </rPr>
-      <t>https://leetcode.com/problems/number-of-provinces/</t>
-    </r>
-  </si>
-  <si>
     <t>Is Graph Bipartite? (medium)</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/is-graph-bipartite/</t>
     </r>
@@ -2272,11 +2898,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/path-with-minimum-effort/</t>
     </r>
@@ -2289,11 +2920,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/merge-similar-items/</t>
     </r>
@@ -2303,11 +2939,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/132-pattern/</t>
     </r>
@@ -2317,33 +2958,48 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/my-calendar-i/</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/my-calendar-ii/</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>https://leetcode.com/problems/my-calendar-iii/</t>
     </r>
@@ -2352,84 +3008,63 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF0000ff"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF0000ff"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF0000ff"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF1155CC"/>
-      <name val="Calibri, sans-serif"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2441,41 +3076,58 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEECE1"/>
-        <bgColor rgb="FFEEECE1"/>
+        <fgColor rgb="FFeeece1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFffff00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF00FF00"/>
+        <fgColor rgb="FF00ff00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFffffff"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
+        <fgColor rgb="FF92d050"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFc6c6c6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFc6c6c6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFc6c6c6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFc6c6c6"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2497,72 +3149,94 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="22">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -2589,22 +3263,82 @@
         <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2616,131 +3350,158 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot rev="0" lon="0" lat="0"/>
+            </a:camera>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -2751,21 +3512,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E221"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
-    <col min="2" max="2" width="65.44140625" customWidth="1"/>
-    <col min="3" max="3" width="77.21875" customWidth="1"/>
-    <col min="4" max="4" width="53.109375" customWidth="1"/>
-    <col min="5" max="5" width="30.44140625" customWidth="1"/>
+    <col min="1" max="1" style="21" width="17.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="21" width="65.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="21" width="77.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="21" width="53.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="21" width="30.433571428571426" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2774,7 +3535,7 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2791,7 +3552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="6"/>
       <c r="B3" s="7" t="s">
         <v>6</v>
@@ -2800,7 +3561,7 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="6"/>
       <c r="B4" s="9" t="s">
         <v>7</v>
@@ -2811,7 +3572,7 @@
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="6"/>
       <c r="B5" s="9" t="s">
         <v>9</v>
@@ -2819,10 +3580,10 @@
       <c r="C5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1">
+      <c r="D5" s="9"/>
+      <c r="E5" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="6"/>
       <c r="B6" s="9" t="s">
         <v>11</v>
@@ -2837,18 +3598,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="6"/>
       <c r="B7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="6"/>
       <c r="B8" s="9" t="s">
         <v>17</v>
@@ -2859,7 +3620,7 @@
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="6"/>
       <c r="B9" s="9" t="s">
         <v>19</v>
@@ -2870,7 +3631,7 @@
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="6"/>
       <c r="B10" s="9" t="s">
         <v>21</v>
@@ -2881,7 +3642,7 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="6"/>
       <c r="B11" s="6" t="s">
         <v>23</v>
@@ -2892,7 +3653,7 @@
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="6"/>
       <c r="B12" s="9" t="s">
         <v>25</v>
@@ -2903,9 +3664,9 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="6"/>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="11" t="s">
@@ -2914,7 +3675,7 @@
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
         <v>29</v>
@@ -2925,7 +3686,7 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="6"/>
       <c r="B15" s="6" t="s">
         <v>31</v>
@@ -2933,12 +3694,12 @@
       <c r="C15" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="24"/>
-    </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1">
+      <c r="E15" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="6"/>
       <c r="B16" s="7" t="s">
         <v>34</v>
@@ -2947,7 +3708,7 @@
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="6"/>
       <c r="B17" s="9" t="s">
         <v>35</v>
@@ -2958,7 +3719,7 @@
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="6"/>
       <c r="B18" s="9" t="s">
         <v>37</v>
@@ -2969,7 +3730,7 @@
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="6"/>
       <c r="B19" s="9" t="s">
         <v>39</v>
@@ -2980,7 +3741,7 @@
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
     </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="6"/>
       <c r="B20" s="9" t="s">
         <v>41</v>
@@ -2991,7 +3752,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
     </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="6"/>
       <c r="B21" s="9" t="s">
         <v>43</v>
@@ -3002,7 +3763,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="15.75">
       <c r="A22" s="6"/>
       <c r="B22" s="6" t="s">
         <v>45</v>
@@ -3013,7 +3774,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
     </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="15.75">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
         <v>47</v>
@@ -3024,7 +3785,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
     </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="15.75">
       <c r="A24" s="6"/>
       <c r="B24" s="6" t="s">
         <v>49</v>
@@ -3035,7 +3796,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
     </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="15.75">
       <c r="A25" s="6"/>
       <c r="B25" s="7" t="s">
         <v>51</v>
@@ -3044,18 +3805,18 @@
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="15.75">
       <c r="A26" s="6"/>
       <c r="B26" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="15" t="s">
         <v>53</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
     </row>
-    <row r="27" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
         <v>54</v>
@@ -3066,7 +3827,7 @@
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
         <v>56</v>
@@ -3077,7 +3838,7 @@
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
     </row>
-    <row r="29" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="6"/>
       <c r="B29" s="9" t="s">
         <v>58</v>
@@ -3088,7 +3849,7 @@
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="6"/>
       <c r="B30" s="9" t="s">
         <v>60</v>
@@ -3099,7 +3860,7 @@
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="6"/>
       <c r="B31" s="9" t="s">
         <v>62</v>
@@ -3110,7 +3871,7 @@
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="6"/>
       <c r="B32" s="9" t="s">
         <v>64</v>
@@ -3121,7 +3882,7 @@
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
     </row>
-    <row r="33" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="6"/>
       <c r="B33" s="9" t="s">
         <v>66</v>
@@ -3132,7 +3893,7 @@
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
     </row>
-    <row r="34" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="6"/>
       <c r="B34" s="9" t="s">
         <v>67</v>
@@ -3143,7 +3904,7 @@
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
     </row>
-    <row r="35" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="6"/>
       <c r="B35" s="6" t="s">
         <v>69</v>
@@ -3154,7 +3915,7 @@
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
     </row>
-    <row r="36" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="6"/>
       <c r="B36" s="6" t="s">
         <v>71</v>
@@ -3165,18 +3926,18 @@
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
     </row>
-    <row r="37" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="6"/>
       <c r="B37" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="12" t="s">
         <v>74</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
     </row>
-    <row r="38" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="6"/>
       <c r="B38" s="7" t="s">
         <v>75</v>
@@ -3185,73 +3946,73 @@
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
     </row>
-    <row r="39" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="6"/>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="15" t="s">
         <v>77</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
     </row>
-    <row r="40" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="6"/>
       <c r="B40" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="15" t="s">
         <v>79</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
     </row>
-    <row r="41" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="6"/>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="15" t="s">
         <v>81</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
     </row>
-    <row r="42" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="6"/>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="15" t="s">
         <v>83</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
     </row>
-    <row r="43" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="6"/>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="15" t="s">
         <v>85</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
     </row>
-    <row r="44" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="6"/>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="15" t="s">
         <v>87</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
     </row>
-    <row r="45" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="6"/>
       <c r="B45" s="7" t="s">
         <v>88</v>
@@ -3260,73 +4021,73 @@
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
     </row>
-    <row r="46" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="6"/>
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="15" t="s">
         <v>90</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
     </row>
-    <row r="47" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="6"/>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="15" t="s">
         <v>92</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
-    <row r="48" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="6"/>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="15" t="s">
         <v>94</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
     </row>
-    <row r="49" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="6"/>
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="15" t="s">
         <v>96</v>
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
-    <row r="50" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="6"/>
-      <c r="B50" s="18" t="s">
+      <c r="B50" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="15" t="s">
         <v>98</v>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
     </row>
-    <row r="51" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="6"/>
-      <c r="B51" s="18" t="s">
+      <c r="B51" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="15" t="s">
         <v>100</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
     </row>
-    <row r="52" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="6"/>
       <c r="B52" s="7" t="s">
         <v>101</v>
@@ -3335,7 +4096,7 @@
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
     </row>
-    <row r="53" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="6"/>
       <c r="B53" s="9" t="s">
         <v>102</v>
@@ -3346,7 +4107,7 @@
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
     </row>
-    <row r="54" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="6"/>
       <c r="B54" s="9" t="s">
         <v>104</v>
@@ -3357,7 +4118,7 @@
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
     </row>
-    <row r="55" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="6"/>
       <c r="B55" s="9" t="s">
         <v>106</v>
@@ -3368,18 +4129,18 @@
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
     </row>
-    <row r="56" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="6"/>
       <c r="B56" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D56" s="24"/>
+      <c r="D56" s="14"/>
       <c r="E56" s="8"/>
     </row>
-    <row r="57" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="6"/>
       <c r="B57" s="9" t="s">
         <v>110</v>
@@ -3390,7 +4151,7 @@
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
     </row>
-    <row r="58" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="6"/>
       <c r="B58" s="6" t="s">
         <v>112</v>
@@ -3401,7 +4162,7 @@
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
     </row>
-    <row r="59" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="6"/>
       <c r="B59" s="6" t="s">
         <v>114</v>
@@ -3412,7 +4173,7 @@
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
     </row>
-    <row r="60" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="6"/>
       <c r="B60" s="7" t="s">
         <v>116</v>
@@ -3421,18 +4182,18 @@
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
     </row>
-    <row r="61" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="6"/>
       <c r="B61" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D61" s="24"/>
+      <c r="D61" s="14"/>
       <c r="E61" s="8"/>
     </row>
-    <row r="62" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="6"/>
       <c r="B62" s="6" t="s">
         <v>119</v>
@@ -3443,7 +4204,7 @@
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
     </row>
-    <row r="63" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="6"/>
       <c r="B63" s="6" t="s">
         <v>121</v>
@@ -3454,7 +4215,7 @@
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
     </row>
-    <row r="64" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="6"/>
       <c r="B64" s="6" t="s">
         <v>123</v>
@@ -3465,7 +4226,7 @@
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
     </row>
-    <row r="65" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="6"/>
       <c r="B65" s="6" t="s">
         <v>125</v>
@@ -3476,7 +4237,7 @@
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
     </row>
-    <row r="66" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="6"/>
       <c r="B66" s="6" t="s">
         <v>127</v>
@@ -3487,7 +4248,7 @@
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
     </row>
-    <row r="67" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="6"/>
       <c r="B67" s="6" t="s">
         <v>129</v>
@@ -3498,7 +4259,7 @@
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
     </row>
-    <row r="68" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="6"/>
       <c r="B68" s="6" t="s">
         <v>131</v>
@@ -3509,7 +4270,7 @@
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
     </row>
-    <row r="69" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="6"/>
       <c r="B69" s="7" t="s">
         <v>133</v>
@@ -3518,7 +4279,7 @@
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
     </row>
-    <row r="70" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="6"/>
       <c r="B70" s="6" t="s">
         <v>134</v>
@@ -3529,7 +4290,7 @@
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
     </row>
-    <row r="71" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="6"/>
       <c r="B71" s="6" t="s">
         <v>136</v>
@@ -3540,7 +4301,7 @@
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
     </row>
-    <row r="72" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="6"/>
       <c r="B72" s="6" t="s">
         <v>138</v>
@@ -3551,7 +4312,7 @@
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
     </row>
-    <row r="73" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="6"/>
       <c r="B73" s="6" t="s">
         <v>140</v>
@@ -3562,7 +4323,7 @@
       <c r="D73" s="8"/>
       <c r="E73" s="8"/>
     </row>
-    <row r="74" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="6"/>
       <c r="B74" s="6" t="s">
         <v>142</v>
@@ -3573,7 +4334,7 @@
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
     </row>
-    <row r="75" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="6"/>
       <c r="B75" s="7" t="s">
         <v>144</v>
@@ -3582,9 +4343,9 @@
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
     </row>
-    <row r="76" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="6"/>
-      <c r="B76" s="19" t="s">
+      <c r="B76" s="18" t="s">
         <v>145</v>
       </c>
       <c r="C76" s="11" t="s">
@@ -3593,7 +4354,7 @@
       <c r="D76" s="8"/>
       <c r="E76" s="8"/>
     </row>
-    <row r="77" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="6"/>
       <c r="B77" s="9" t="s">
         <v>147</v>
@@ -3604,7 +4365,7 @@
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
     </row>
-    <row r="78" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="6"/>
       <c r="B78" s="9" t="s">
         <v>149</v>
@@ -3613,7 +4374,7 @@
       <c r="D78" s="8"/>
       <c r="E78" s="8"/>
     </row>
-    <row r="79" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="6"/>
       <c r="B79" s="9" t="s">
         <v>150</v>
@@ -3621,10 +4382,10 @@
       <c r="C79" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-    </row>
-    <row r="80" spans="1:5" ht="14.4">
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="6"/>
       <c r="B80" s="9" t="s">
         <v>152</v>
@@ -3635,7 +4396,7 @@
       <c r="D80" s="8"/>
       <c r="E80" s="8"/>
     </row>
-    <row r="81" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="6"/>
       <c r="B81" s="6" t="s">
         <v>154</v>
@@ -3646,7 +4407,7 @@
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
     </row>
-    <row r="82" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="6"/>
       <c r="B82" s="9" t="s">
         <v>156</v>
@@ -3657,7 +4418,7 @@
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
     </row>
-    <row r="83" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="6"/>
       <c r="B83" s="6" t="s">
         <v>158</v>
@@ -3668,7 +4429,7 @@
       <c r="D83" s="8"/>
       <c r="E83" s="8"/>
     </row>
-    <row r="84" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="6"/>
       <c r="B84" s="6" t="s">
         <v>160</v>
@@ -3679,7 +4440,7 @@
       <c r="D84" s="8"/>
       <c r="E84" s="8"/>
     </row>
-    <row r="85" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="6"/>
       <c r="B85" s="7" t="s">
         <v>162</v>
@@ -3688,7 +4449,7 @@
       <c r="D85" s="8"/>
       <c r="E85" s="8"/>
     </row>
-    <row r="86" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="6"/>
       <c r="B86" s="6" t="s">
         <v>163</v>
@@ -3699,7 +4460,7 @@
       <c r="D86" s="8"/>
       <c r="E86" s="8"/>
     </row>
-    <row r="87" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="6"/>
       <c r="B87" s="6" t="s">
         <v>165</v>
@@ -3710,7 +4471,7 @@
       <c r="D87" s="8"/>
       <c r="E87" s="8"/>
     </row>
-    <row r="88" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="6"/>
       <c r="B88" s="6" t="s">
         <v>167</v>
@@ -3721,7 +4482,7 @@
       <c r="D88" s="8"/>
       <c r="E88" s="8"/>
     </row>
-    <row r="89" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="6"/>
       <c r="B89" s="6" t="s">
         <v>169</v>
@@ -3732,7 +4493,7 @@
       <c r="D89" s="8"/>
       <c r="E89" s="8"/>
     </row>
-    <row r="90" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="6"/>
       <c r="B90" s="6" t="s">
         <v>171</v>
@@ -3743,7 +4504,7 @@
       <c r="D90" s="8"/>
       <c r="E90" s="8"/>
     </row>
-    <row r="91" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="6"/>
       <c r="B91" s="7" t="s">
         <v>173</v>
@@ -3752,7 +4513,7 @@
       <c r="D91" s="8"/>
       <c r="E91" s="8"/>
     </row>
-    <row r="92" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="6"/>
       <c r="B92" s="6" t="s">
         <v>174</v>
@@ -3763,7 +4524,7 @@
       <c r="D92" s="8"/>
       <c r="E92" s="8"/>
     </row>
-    <row r="93" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="6"/>
       <c r="B93" s="6" t="s">
         <v>176</v>
@@ -3774,7 +4535,7 @@
       <c r="D93" s="8"/>
       <c r="E93" s="8"/>
     </row>
-    <row r="94" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="6"/>
       <c r="B94" s="6" t="s">
         <v>178</v>
@@ -3785,7 +4546,7 @@
       <c r="D94" s="8"/>
       <c r="E94" s="8"/>
     </row>
-    <row r="95" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="6"/>
       <c r="B95" s="6" t="s">
         <v>180</v>
@@ -3796,7 +4557,7 @@
       <c r="D95" s="8"/>
       <c r="E95" s="8"/>
     </row>
-    <row r="96" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="6"/>
       <c r="B96" s="6" t="s">
         <v>182</v>
@@ -3807,7 +4568,7 @@
       <c r="D96" s="8"/>
       <c r="E96" s="8"/>
     </row>
-    <row r="97" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="6"/>
       <c r="B97" s="6" t="s">
         <v>184</v>
@@ -3818,7 +4579,7 @@
       <c r="D97" s="8"/>
       <c r="E97" s="8"/>
     </row>
-    <row r="98" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="6"/>
       <c r="B98" s="6" t="s">
         <v>186</v>
@@ -3829,7 +4590,7 @@
       <c r="D98" s="8"/>
       <c r="E98" s="8"/>
     </row>
-    <row r="99" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="6"/>
       <c r="B99" s="6" t="s">
         <v>188</v>
@@ -3840,7 +4601,7 @@
       <c r="D99" s="8"/>
       <c r="E99" s="8"/>
     </row>
-    <row r="100" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="6"/>
       <c r="B100" s="6" t="s">
         <v>190</v>
@@ -3851,7 +4612,7 @@
       <c r="D100" s="8"/>
       <c r="E100" s="8"/>
     </row>
-    <row r="101" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="6"/>
       <c r="B101" s="6" t="s">
         <v>192</v>
@@ -3862,16 +4623,16 @@
       <c r="D101" s="8"/>
       <c r="E101" s="8"/>
     </row>
-    <row r="102" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="6"/>
-      <c r="B102" s="20" t="s">
+      <c r="B102" s="19" t="s">
         <v>194</v>
       </c>
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
       <c r="E102" s="8"/>
     </row>
-    <row r="103" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
       <c r="A103" s="6"/>
       <c r="B103" s="6" t="s">
         <v>195</v>
@@ -3882,7 +4643,7 @@
       <c r="D103" s="8"/>
       <c r="E103" s="8"/>
     </row>
-    <row r="104" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
       <c r="A104" s="6"/>
       <c r="B104" s="6" t="s">
         <v>197</v>
@@ -3893,7 +4654,7 @@
       <c r="D104" s="8"/>
       <c r="E104" s="8"/>
     </row>
-    <row r="105" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
       <c r="A105" s="6"/>
       <c r="B105" s="6" t="s">
         <v>199</v>
@@ -3904,7 +4665,7 @@
       <c r="D105" s="8"/>
       <c r="E105" s="8"/>
     </row>
-    <row r="106" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
       <c r="A106" s="6"/>
       <c r="B106" s="6" t="s">
         <v>201</v>
@@ -3915,1389 +4676,1211 @@
       <c r="D106" s="8"/>
       <c r="E106" s="8"/>
     </row>
-    <row r="107" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
       <c r="A107" s="6"/>
       <c r="B107" s="6" t="s">
         <v>203</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D107" s="8"/>
       <c r="E107" s="8"/>
     </row>
-    <row r="108" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
       <c r="A108" s="6"/>
       <c r="B108" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C108" s="11" t="s">
         <v>205</v>
-      </c>
-      <c r="C108" s="11" t="s">
-        <v>206</v>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="8"/>
     </row>
-    <row r="109" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
       <c r="A109" s="6"/>
       <c r="B109" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C109" s="11" t="s">
         <v>207</v>
-      </c>
-      <c r="C109" s="11" t="s">
-        <v>208</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8"/>
     </row>
-    <row r="110" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="6"/>
-      <c r="B110" s="20" t="s">
-        <v>209</v>
+      <c r="B110" s="19" t="s">
+        <v>208</v>
       </c>
       <c r="C110" s="8"/>
       <c r="D110" s="8"/>
       <c r="E110" s="8"/>
     </row>
-    <row r="111" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
       <c r="A111" s="6"/>
       <c r="B111" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C111" s="8"/>
       <c r="D111" s="8"/>
       <c r="E111" s="8"/>
     </row>
-    <row r="112" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
       <c r="A112" s="6"/>
       <c r="B112" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C112" s="8"/>
       <c r="D112" s="8"/>
       <c r="E112" s="8"/>
     </row>
-    <row r="113" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
       <c r="A113" s="6"/>
       <c r="B113" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C113" s="11" t="s">
         <v>212</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>213</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
     </row>
-    <row r="114" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
       <c r="A114" s="6"/>
       <c r="B114" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C114" s="11" t="s">
         <v>214</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>215</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8"/>
     </row>
-    <row r="115" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
       <c r="A115" s="6"/>
       <c r="B115" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C115" s="11" t="s">
         <v>216</v>
-      </c>
-      <c r="C115" s="11" t="s">
-        <v>217</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8"/>
     </row>
-    <row r="116" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
       <c r="A116" s="6"/>
-      <c r="B116" s="20" t="s">
-        <v>218</v>
+      <c r="B116" s="19" t="s">
+        <v>217</v>
       </c>
       <c r="C116" s="8"/>
       <c r="D116" s="8"/>
       <c r="E116" s="8"/>
     </row>
-    <row r="117" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
       <c r="A117" s="6"/>
       <c r="B117" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C117" s="11" t="s">
         <v>219</v>
-      </c>
-      <c r="C117" s="11" t="s">
-        <v>220</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8"/>
     </row>
-    <row r="118" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
       <c r="A118" s="6"/>
       <c r="B118" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C118" s="8"/>
       <c r="D118" s="8"/>
       <c r="E118" s="8"/>
     </row>
-    <row r="119" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
       <c r="A119" s="6"/>
       <c r="B119" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C119" s="11" t="s">
         <v>222</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>223</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8"/>
     </row>
-    <row r="120" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
       <c r="A120" s="6"/>
       <c r="B120" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C120" s="11" t="s">
         <v>224</v>
-      </c>
-      <c r="C120" s="11" t="s">
-        <v>225</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8"/>
     </row>
-    <row r="121" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
       <c r="A121" s="6"/>
       <c r="B121" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C121" s="8"/>
       <c r="D121" s="8"/>
       <c r="E121" s="8"/>
     </row>
-    <row r="122" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
       <c r="A122" s="6"/>
       <c r="B122" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C122" s="8"/>
       <c r="D122" s="8"/>
       <c r="E122" s="8"/>
     </row>
-    <row r="123" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
       <c r="A123" s="6"/>
       <c r="B123" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C123" s="8"/>
       <c r="D123" s="8"/>
       <c r="E123" s="8"/>
     </row>
-    <row r="124" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
       <c r="A124" s="6"/>
-      <c r="B124" s="20" t="s">
-        <v>229</v>
+      <c r="B124" s="19" t="s">
+        <v>228</v>
       </c>
       <c r="C124" s="8"/>
       <c r="D124" s="8"/>
       <c r="E124" s="8"/>
     </row>
-    <row r="125" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
       <c r="A125" s="6"/>
       <c r="B125" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C125" s="11" t="s">
         <v>230</v>
-      </c>
-      <c r="C125" s="11" t="s">
-        <v>231</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8"/>
     </row>
-    <row r="126" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
       <c r="A126" s="6"/>
       <c r="B126" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C126" s="11" t="s">
         <v>232</v>
-      </c>
-      <c r="C126" s="11" t="s">
-        <v>233</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8"/>
     </row>
-    <row r="127" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
       <c r="A127" s="6"/>
       <c r="B127" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C127" s="11" t="s">
         <v>234</v>
-      </c>
-      <c r="C127" s="11" t="s">
-        <v>235</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8"/>
     </row>
-    <row r="128" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
       <c r="A128" s="6"/>
       <c r="B128" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C128" s="11" t="s">
         <v>236</v>
-      </c>
-      <c r="C128" s="11" t="s">
-        <v>237</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="8"/>
     </row>
-    <row r="129" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
       <c r="A129" s="6"/>
-      <c r="B129" s="20" t="s">
-        <v>238</v>
+      <c r="B129" s="19" t="s">
+        <v>237</v>
       </c>
       <c r="C129" s="8"/>
       <c r="D129" s="8"/>
       <c r="E129" s="8"/>
     </row>
-    <row r="130" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
       <c r="A130" s="6"/>
       <c r="B130" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C130" s="11" t="s">
         <v>239</v>
-      </c>
-      <c r="C130" s="11" t="s">
-        <v>240</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8"/>
     </row>
-    <row r="131" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
       <c r="A131" s="6"/>
       <c r="B131" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C131" s="11" t="s">
         <v>241</v>
-      </c>
-      <c r="C131" s="11" t="s">
-        <v>242</v>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8"/>
     </row>
-    <row r="132" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
       <c r="A132" s="6"/>
       <c r="B132" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C132" s="11" t="s">
         <v>243</v>
-      </c>
-      <c r="C132" s="11" t="s">
-        <v>244</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8"/>
     </row>
-    <row r="133" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
       <c r="A133" s="6"/>
       <c r="B133" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C133" s="8"/>
       <c r="D133" s="8"/>
       <c r="E133" s="8"/>
     </row>
-    <row r="134" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
       <c r="A134" s="6"/>
       <c r="B134" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C134" s="8"/>
       <c r="D134" s="8"/>
       <c r="E134" s="8"/>
     </row>
-    <row r="135" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
       <c r="A135" s="6"/>
       <c r="B135" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C135" s="11" t="s">
         <v>247</v>
-      </c>
-      <c r="C135" s="11" t="s">
-        <v>248</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8"/>
     </row>
-    <row r="136" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
       <c r="A136" s="6"/>
-      <c r="B136" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="C136" s="21"/>
+      <c r="B136" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="C136" s="20"/>
       <c r="D136" s="8"/>
       <c r="E136" s="8"/>
     </row>
-    <row r="137" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
       <c r="A137" s="6"/>
       <c r="B137" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C137" s="11" t="s">
         <v>250</v>
-      </c>
-      <c r="C137" s="11" t="s">
-        <v>251</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8"/>
     </row>
-    <row r="138" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
       <c r="A138" s="6"/>
       <c r="B138" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C138" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="C138" s="11" t="s">
+      <c r="D138" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="D138" s="11" t="s">
-        <v>254</v>
-      </c>
       <c r="E138" s="8"/>
     </row>
-    <row r="139" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
       <c r="A139" s="6"/>
       <c r="B139" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C139" s="11" t="s">
         <v>255</v>
-      </c>
-      <c r="C139" s="11" t="s">
-        <v>256</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8"/>
     </row>
-    <row r="140" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
       <c r="A140" s="6"/>
       <c r="B140" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C140" s="11" t="s">
         <v>257</v>
-      </c>
-      <c r="C140" s="11" t="s">
-        <v>258</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8"/>
     </row>
-    <row r="141" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
       <c r="A141" s="6"/>
       <c r="B141" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C141" s="11" t="s">
         <v>259</v>
-      </c>
-      <c r="C141" s="11" t="s">
-        <v>260</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8"/>
     </row>
-    <row r="142" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
       <c r="A142" s="6"/>
       <c r="B142" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C142" s="8"/>
       <c r="D142" s="8"/>
       <c r="E142" s="8"/>
     </row>
-    <row r="143" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
       <c r="A143" s="6"/>
       <c r="B143" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C143" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="C143" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="D143" s="24"/>
+      <c r="D143" s="14"/>
       <c r="E143" s="8"/>
     </row>
-    <row r="144" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
       <c r="A144" s="6"/>
       <c r="B144" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C144" s="11" t="s">
         <v>264</v>
-      </c>
-      <c r="C144" s="11" t="s">
-        <v>265</v>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="8"/>
     </row>
-    <row r="145" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
       <c r="A145" s="6"/>
       <c r="B145" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C145" s="11" t="s">
         <v>266</v>
-      </c>
-      <c r="C145" s="11" t="s">
-        <v>267</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8"/>
     </row>
-    <row r="146" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
       <c r="A146" s="6"/>
       <c r="B146" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C146" s="11" t="s">
         <v>268</v>
-      </c>
-      <c r="C146" s="11" t="s">
-        <v>269</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8"/>
     </row>
-    <row r="147" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
       <c r="A147" s="6"/>
       <c r="B147" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C147" s="11" t="s">
         <v>270</v>
-      </c>
-      <c r="C147" s="11" t="s">
-        <v>271</v>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8"/>
     </row>
-    <row r="148" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
       <c r="A148" s="6"/>
       <c r="B148" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C148" s="11" t="s">
         <v>272</v>
-      </c>
-      <c r="C148" s="11" t="s">
-        <v>273</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8"/>
     </row>
-    <row r="149" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
       <c r="A149" s="6"/>
       <c r="B149" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C149" s="11" t="s">
         <v>274</v>
-      </c>
-      <c r="C149" s="11" t="s">
-        <v>275</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8"/>
     </row>
-    <row r="150" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
       <c r="A150" s="6"/>
       <c r="B150" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C150" s="11" t="s">
         <v>276</v>
-      </c>
-      <c r="C150" s="11" t="s">
-        <v>277</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8"/>
     </row>
-    <row r="151" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
       <c r="A151" s="6"/>
       <c r="B151" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C151" s="11" t="s">
         <v>278</v>
-      </c>
-      <c r="C151" s="11" t="s">
-        <v>279</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8"/>
     </row>
-    <row r="152" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
       <c r="A152" s="6"/>
-      <c r="B152" s="20" t="s">
-        <v>280</v>
+      <c r="B152" s="19" t="s">
+        <v>279</v>
       </c>
       <c r="C152" s="8"/>
       <c r="D152" s="8"/>
       <c r="E152" s="8"/>
     </row>
-    <row r="153" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
       <c r="A153" s="6"/>
       <c r="B153" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C153" s="8"/>
       <c r="D153" s="8"/>
       <c r="E153" s="8"/>
     </row>
-    <row r="154" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
       <c r="A154" s="6"/>
       <c r="B154" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C154" s="8"/>
       <c r="D154" s="8"/>
       <c r="E154" s="8"/>
     </row>
-    <row r="155" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
       <c r="A155" s="6"/>
       <c r="B155" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C155" s="8"/>
       <c r="D155" s="8"/>
       <c r="E155" s="8"/>
     </row>
-    <row r="156" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
       <c r="A156" s="6"/>
       <c r="B156" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C156" s="8"/>
       <c r="D156" s="8"/>
       <c r="E156" s="8"/>
     </row>
-    <row r="157" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
       <c r="A157" s="6"/>
-      <c r="B157" s="20" t="s">
-        <v>285</v>
+      <c r="B157" s="19" t="s">
+        <v>284</v>
       </c>
       <c r="C157" s="8"/>
       <c r="D157" s="8"/>
       <c r="E157" s="8"/>
     </row>
-    <row r="158" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
       <c r="A158" s="6"/>
       <c r="B158" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C158" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="C158" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="D158" s="24"/>
+      <c r="D158" s="14"/>
       <c r="E158" s="8"/>
     </row>
-    <row r="159" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
       <c r="A159" s="6"/>
       <c r="B159" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C159" s="8"/>
       <c r="D159" s="8"/>
       <c r="E159" s="8"/>
     </row>
-    <row r="160" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
       <c r="A160" s="6"/>
-      <c r="B160" s="22" t="s">
+      <c r="B160" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C160" s="11" t="s">
         <v>289</v>
-      </c>
-      <c r="C160" s="11" t="s">
-        <v>290</v>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="8"/>
     </row>
-    <row r="161" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
       <c r="A161" s="6"/>
       <c r="B161" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C161" s="8"/>
       <c r="D161" s="8"/>
       <c r="E161" s="8"/>
     </row>
-    <row r="162" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
       <c r="A162" s="6"/>
       <c r="B162" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C162" s="8"/>
       <c r="D162" s="8"/>
       <c r="E162" s="8"/>
     </row>
-    <row r="163" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
       <c r="A163" s="6"/>
       <c r="B163" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C163" s="8"/>
       <c r="D163" s="8"/>
       <c r="E163" s="8"/>
     </row>
-    <row r="164" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
       <c r="A164" s="6"/>
       <c r="B164" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="C164" s="11" t="s">
         <v>294</v>
-      </c>
-      <c r="C164" s="11" t="s">
-        <v>295</v>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8"/>
     </row>
-    <row r="165" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
       <c r="A165" s="6"/>
-      <c r="B165" s="22" t="s">
-        <v>296</v>
+      <c r="B165" s="6" t="s">
+        <v>295</v>
       </c>
       <c r="C165" s="8"/>
       <c r="D165" s="8"/>
       <c r="E165" s="8"/>
     </row>
-    <row r="166" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
       <c r="A166" s="6"/>
       <c r="B166" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C166" s="8"/>
       <c r="D166" s="8"/>
       <c r="E166" s="8"/>
     </row>
-    <row r="167" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
       <c r="A167" s="6"/>
       <c r="B167" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C167" s="8"/>
       <c r="D167" s="8"/>
       <c r="E167" s="8"/>
     </row>
-    <row r="168" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
       <c r="A168" s="6"/>
       <c r="B168" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C168" s="8"/>
       <c r="D168" s="8"/>
       <c r="E168" s="8"/>
     </row>
-    <row r="169" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75">
       <c r="A169" s="6"/>
       <c r="B169" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C169" s="8"/>
       <c r="D169" s="8"/>
       <c r="E169" s="8"/>
     </row>
-    <row r="170" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75">
       <c r="A170" s="6"/>
       <c r="B170" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C170" s="8"/>
       <c r="D170" s="8"/>
       <c r="E170" s="8"/>
     </row>
-    <row r="171" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75">
       <c r="A171" s="6"/>
       <c r="B171" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C171" s="8"/>
       <c r="D171" s="8"/>
       <c r="E171" s="8"/>
     </row>
-    <row r="172" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75">
       <c r="A172" s="6"/>
       <c r="B172" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C172" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="C172" s="23" t="s">
+      <c r="D172" s="14"/>
+      <c r="E172" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75">
+      <c r="A173" s="6"/>
+      <c r="B173" s="19" t="s">
         <v>304</v>
-      </c>
-      <c r="D172" s="24"/>
-      <c r="E172" s="8"/>
-    </row>
-    <row r="173" spans="1:5" ht="14.4">
-      <c r="A173" s="6"/>
-      <c r="B173" s="20" t="s">
-        <v>305</v>
       </c>
       <c r="C173" s="8"/>
       <c r="D173" s="8"/>
       <c r="E173" s="8"/>
     </row>
-    <row r="174" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75">
       <c r="A174" s="6"/>
       <c r="B174" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="C174" s="11" t="s">
         <v>306</v>
-      </c>
-      <c r="C174" s="11" t="s">
-        <v>307</v>
       </c>
       <c r="D174" s="8"/>
       <c r="E174" s="8"/>
     </row>
-    <row r="175" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75">
       <c r="A175" s="6"/>
       <c r="B175" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C175" s="11" t="s">
         <v>308</v>
-      </c>
-      <c r="C175" s="11" t="s">
-        <v>309</v>
       </c>
       <c r="D175" s="8"/>
       <c r="E175" s="8"/>
     </row>
-    <row r="176" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="18.75">
       <c r="A176" s="6"/>
       <c r="B176" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C176" s="11" t="s">
         <v>310</v>
-      </c>
-      <c r="C176" s="11" t="s">
-        <v>311</v>
       </c>
       <c r="D176" s="8"/>
       <c r="E176" s="8"/>
     </row>
-    <row r="177" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="18.75">
       <c r="A177" s="6"/>
       <c r="B177" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="C177" s="11" t="s">
         <v>312</v>
-      </c>
-      <c r="C177" s="11" t="s">
-        <v>313</v>
       </c>
       <c r="D177" s="8"/>
       <c r="E177" s="8"/>
     </row>
-    <row r="178" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18.75">
       <c r="A178" s="6"/>
       <c r="B178" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C178" s="8"/>
       <c r="D178" s="8"/>
       <c r="E178" s="8"/>
     </row>
-    <row r="179" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="18.75">
       <c r="A179" s="6"/>
-      <c r="B179" s="20" t="s">
-        <v>315</v>
+      <c r="B179" s="19" t="s">
+        <v>314</v>
       </c>
       <c r="C179" s="8"/>
       <c r="D179" s="8"/>
       <c r="E179" s="8"/>
     </row>
-    <row r="180" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18.75">
       <c r="A180" s="6"/>
       <c r="B180" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C180" s="11" t="s">
         <v>316</v>
-      </c>
-      <c r="C180" s="11" t="s">
-        <v>317</v>
       </c>
       <c r="D180" s="8"/>
       <c r="E180" s="8"/>
     </row>
-    <row r="181" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18.75">
       <c r="A181" s="6"/>
       <c r="B181" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="C181" s="11" t="s">
         <v>318</v>
-      </c>
-      <c r="C181" s="11" t="s">
-        <v>319</v>
       </c>
       <c r="D181" s="8"/>
       <c r="E181" s="8"/>
     </row>
-    <row r="182" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="18.75">
       <c r="A182" s="6"/>
       <c r="B182" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="C182" s="11" t="s">
         <v>320</v>
-      </c>
-      <c r="C182" s="11" t="s">
-        <v>321</v>
       </c>
       <c r="D182" s="8"/>
       <c r="E182" s="8"/>
     </row>
-    <row r="183" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18.75">
       <c r="A183" s="6"/>
       <c r="B183" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C183" s="11" t="s">
         <v>322</v>
-      </c>
-      <c r="C183" s="11" t="s">
-        <v>323</v>
       </c>
       <c r="D183" s="8"/>
       <c r="E183" s="8"/>
     </row>
-    <row r="184" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="18.75">
       <c r="A184" s="6"/>
       <c r="B184" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C184" s="11" t="s">
         <v>324</v>
-      </c>
-      <c r="C184" s="11" t="s">
-        <v>325</v>
       </c>
       <c r="D184" s="8"/>
       <c r="E184" s="8"/>
     </row>
-    <row r="185" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75">
       <c r="A185" s="6"/>
       <c r="B185" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C185" s="11" t="s">
         <v>326</v>
-      </c>
-      <c r="C185" s="11" t="s">
-        <v>327</v>
       </c>
       <c r="D185" s="8"/>
       <c r="E185" s="8"/>
     </row>
-    <row r="186" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18.75">
       <c r="A186" s="6"/>
-      <c r="B186" s="20" t="s">
-        <v>328</v>
+      <c r="B186" s="19" t="s">
+        <v>327</v>
       </c>
       <c r="C186" s="8"/>
       <c r="D186" s="8"/>
       <c r="E186" s="8"/>
     </row>
-    <row r="187" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18.75">
       <c r="A187" s="6"/>
       <c r="B187" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="C187" s="11" t="s">
         <v>329</v>
-      </c>
-      <c r="C187" s="11" t="s">
-        <v>330</v>
       </c>
       <c r="D187" s="8"/>
       <c r="E187" s="8"/>
     </row>
-    <row r="188" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="18.75">
       <c r="A188" s="6"/>
       <c r="B188" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C188" s="11" t="s">
         <v>331</v>
-      </c>
-      <c r="C188" s="11" t="s">
-        <v>332</v>
       </c>
       <c r="D188" s="8"/>
       <c r="E188" s="8"/>
     </row>
-    <row r="189" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="18.75">
       <c r="A189" s="6"/>
       <c r="B189" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C189" s="11" t="s">
         <v>333</v>
-      </c>
-      <c r="C189" s="11" t="s">
-        <v>334</v>
       </c>
       <c r="D189" s="8"/>
       <c r="E189" s="8"/>
     </row>
-    <row r="190" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="18.75">
       <c r="A190" s="6"/>
       <c r="B190" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C190" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="C190" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="D190" s="24"/>
+      <c r="D190" s="14"/>
       <c r="E190" s="8"/>
     </row>
-    <row r="191" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="18.75">
       <c r="A191" s="6"/>
       <c r="B191" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C191" s="8"/>
       <c r="D191" s="8"/>
       <c r="E191" s="8"/>
     </row>
-    <row r="192" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="18.75">
       <c r="A192" s="6"/>
       <c r="B192" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C192" s="8"/>
       <c r="D192" s="8"/>
       <c r="E192" s="8"/>
     </row>
-    <row r="193" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="18.75">
       <c r="A193" s="6"/>
-      <c r="B193" s="20" t="s">
-        <v>339</v>
+      <c r="B193" s="19" t="s">
+        <v>338</v>
       </c>
       <c r="C193" s="8"/>
       <c r="D193" s="8"/>
       <c r="E193" s="8"/>
     </row>
-    <row r="194" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="18.75">
       <c r="A194" s="6"/>
       <c r="B194" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C194" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="C194" s="11" t="s">
+      <c r="D194" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="D194" s="11" t="s">
+      <c r="E194" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="E194" s="11" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" ht="14.4">
+    </row>
+    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="18.75">
       <c r="A195" s="6"/>
       <c r="B195" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C195" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="C195" s="11" t="s">
+      <c r="D195" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="D195" s="11" t="s">
-        <v>346</v>
-      </c>
       <c r="E195" s="8"/>
     </row>
-    <row r="196" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="18.75">
       <c r="A196" s="6"/>
       <c r="B196" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="C196" s="11" t="s">
         <v>347</v>
-      </c>
-      <c r="C196" s="11" t="s">
-        <v>348</v>
       </c>
       <c r="D196" s="8"/>
       <c r="E196" s="8"/>
     </row>
-    <row r="197" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="18.75">
       <c r="A197" s="6"/>
       <c r="B197" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C197" s="11" t="s">
         <v>349</v>
-      </c>
-      <c r="C197" s="11" t="s">
-        <v>350</v>
       </c>
       <c r="D197" s="8"/>
       <c r="E197" s="8"/>
     </row>
-    <row r="198" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="18.75">
       <c r="A198" s="6"/>
       <c r="B198" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C198" s="11" t="s">
         <v>351</v>
-      </c>
-      <c r="C198" s="11" t="s">
-        <v>352</v>
       </c>
       <c r="D198" s="8"/>
       <c r="E198" s="8"/>
     </row>
-    <row r="199" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="18.75">
       <c r="A199" s="6"/>
-      <c r="B199" s="20" t="s">
-        <v>353</v>
+      <c r="B199" s="19" t="s">
+        <v>352</v>
       </c>
       <c r="C199" s="8"/>
       <c r="D199" s="8"/>
       <c r="E199" s="8"/>
     </row>
-    <row r="200" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="18.75">
       <c r="A200" s="6"/>
       <c r="B200" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C200" s="11" t="s">
         <v>354</v>
-      </c>
-      <c r="C200" s="11" t="s">
-        <v>355</v>
       </c>
       <c r="D200" s="8"/>
       <c r="E200" s="8"/>
     </row>
-    <row r="201" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="18.75">
       <c r="A201" s="6"/>
       <c r="B201" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C201" s="11" t="s">
         <v>356</v>
-      </c>
-      <c r="C201" s="11" t="s">
-        <v>357</v>
       </c>
       <c r="D201" s="8"/>
       <c r="E201" s="8"/>
     </row>
-    <row r="202" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="18.75">
       <c r="A202" s="6"/>
       <c r="B202" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="C202" s="11" t="s">
         <v>358</v>
-      </c>
-      <c r="C202" s="11" t="s">
-        <v>359</v>
       </c>
       <c r="D202" s="8"/>
       <c r="E202" s="8"/>
     </row>
-    <row r="203" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="18.75">
       <c r="A203" s="6"/>
       <c r="B203" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C203" s="11" t="s">
         <v>360</v>
-      </c>
-      <c r="C203" s="11" t="s">
-        <v>361</v>
       </c>
       <c r="D203" s="8"/>
       <c r="E203" s="8"/>
     </row>
-    <row r="204" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="18.75">
       <c r="A204" s="6"/>
       <c r="B204" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="C204" s="11" t="s">
         <v>362</v>
-      </c>
-      <c r="C204" s="11" t="s">
-        <v>363</v>
       </c>
       <c r="D204" s="8"/>
       <c r="E204" s="8"/>
     </row>
-    <row r="205" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="18.75">
       <c r="A205" s="6"/>
-      <c r="B205" s="20" t="s">
-        <v>364</v>
+      <c r="B205" s="19" t="s">
+        <v>363</v>
       </c>
       <c r="C205" s="8"/>
       <c r="D205" s="8"/>
       <c r="E205" s="8"/>
     </row>
-    <row r="206" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="18.75">
       <c r="A206" s="6"/>
       <c r="B206" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="C206" s="11" t="s">
         <v>365</v>
-      </c>
-      <c r="C206" s="11" t="s">
-        <v>366</v>
       </c>
       <c r="D206" s="8"/>
       <c r="E206" s="8"/>
     </row>
-    <row r="207" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="18.75">
       <c r="A207" s="6"/>
       <c r="B207" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="C207" s="11" t="s">
         <v>367</v>
-      </c>
-      <c r="C207" s="11" t="s">
-        <v>368</v>
       </c>
       <c r="D207" s="8"/>
       <c r="E207" s="8"/>
     </row>
-    <row r="208" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="18.75">
       <c r="A208" s="6"/>
       <c r="B208" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D208" s="8"/>
       <c r="E208" s="8"/>
     </row>
-    <row r="209" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="18.75">
       <c r="A209" s="6"/>
       <c r="B209" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C209" s="11" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D209" s="8"/>
       <c r="E209" s="8"/>
     </row>
-    <row r="210" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="18.75">
       <c r="A210" s="6"/>
       <c r="B210" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C210" s="11" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D210" s="8"/>
       <c r="E210" s="8"/>
     </row>
-    <row r="211" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="18.75">
       <c r="A211" s="6"/>
       <c r="B211" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C211" s="11" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D211" s="8"/>
       <c r="E211" s="8"/>
     </row>
-    <row r="212" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="18.75">
       <c r="A212" s="6"/>
       <c r="B212" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C212" s="11" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D212" s="8"/>
       <c r="E212" s="8"/>
     </row>
-    <row r="213" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="18.75">
       <c r="A213" s="6"/>
-      <c r="B213" s="20" t="s">
-        <v>379</v>
+      <c r="B213" s="19" t="s">
+        <v>377</v>
       </c>
       <c r="C213" s="8"/>
       <c r="D213" s="8"/>
       <c r="E213" s="8"/>
     </row>
-    <row r="214" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="18.75">
       <c r="A214" s="6"/>
       <c r="B214" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="C214" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="D214" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="C214" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="D214" s="11" t="s">
-        <v>382</v>
-      </c>
       <c r="E214" s="8"/>
     </row>
-    <row r="215" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="18.75">
       <c r="A215" s="6"/>
       <c r="B215" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C215" s="11" t="s">
         <v>214</v>
-      </c>
-      <c r="C215" s="11" t="s">
-        <v>383</v>
       </c>
       <c r="D215" s="8"/>
       <c r="E215" s="8"/>
     </row>
-    <row r="216" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="18.75">
       <c r="A216" s="6"/>
       <c r="B216" s="6" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C216" s="11" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D216" s="8"/>
       <c r="E216" s="8"/>
     </row>
-    <row r="217" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="18.75">
       <c r="A217" s="6"/>
       <c r="B217" s="6" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C217" s="11" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D217" s="8"/>
       <c r="E217" s="8"/>
     </row>
-    <row r="218" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="18.75">
       <c r="A218" s="6"/>
-      <c r="B218" s="20" t="s">
-        <v>388</v>
+      <c r="B218" s="19" t="s">
+        <v>385</v>
       </c>
       <c r="C218" s="8"/>
       <c r="D218" s="8"/>
       <c r="E218" s="8"/>
     </row>
-    <row r="219" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="18.75">
       <c r="A219" s="6"/>
       <c r="B219" s="6" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C219" s="11" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D219" s="8"/>
       <c r="E219" s="8"/>
     </row>
-    <row r="220" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="18.75">
       <c r="A220" s="6"/>
       <c r="B220" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C220" s="11" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D220" s="8"/>
       <c r="E220" s="8"/>
     </row>
-    <row r="221" spans="1:5" ht="14.4">
+    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="18.75">
       <c r="A221" s="6"/>
       <c r="B221" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C221" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="D221" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="E221" s="11" t="s">
         <v>393</v>
-      </c>
-      <c r="C221" s="11" t="s">
-        <v>394</v>
-      </c>
-      <c r="D221" s="11" t="s">
-        <v>395</v>
-      </c>
-      <c r="E221" s="11" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="C190:D190"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="C56:D56"/>
     <mergeCell ref="C61:D61"/>
     <mergeCell ref="C143:D143"/>
     <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="C190:D190"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="E6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="C7" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="C8" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="C9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="C10" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="C11" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="C12" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="C13" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="C14" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="C15" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="D15" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="C17" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="C18" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="C19" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="C20" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="C21" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="C22" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="C23" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="C24" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="C26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="C27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="C28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="C29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="C30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="C31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="C32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="C33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="C34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="C35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="C36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="C37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="C39" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="C40" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="C41" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="C42" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="C43" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="C44" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="C46" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="C47" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="C48" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="C49" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="C50" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="C51" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="C53" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="C54" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="C55" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="C56" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="C57" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="C58" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="C59" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="C61" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="C62" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C63" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="C64" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C65" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="C66" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="C67" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="C68" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="C70" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C71" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="C72" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C73" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="C74" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="B76" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="C76" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="C77" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="C79" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="C80" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="C81" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="C82" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="C83" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="C84" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="C86" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="C87" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="C88" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="C89" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="C90" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="C92" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="C93" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="C94" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="C95" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C96" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="C97" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C98" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C99" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C100" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="C101" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="C103" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="C104" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="C105" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="C106" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="C107" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="C108" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="C109" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="C113" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="C114" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="C115" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="C117" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="C119" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="C120" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="C125" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="C126" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="C127" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="C128" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="C130" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="C131" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="C132" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="C135" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="C137" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="C138" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="D138" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="C139" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="C140" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="C141" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="C143" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="C144" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="C145" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="C146" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="C147" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="C148" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="C149" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="C150" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="C151" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="C158" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="C160" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="C164" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="C172" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="C174" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="C175" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="C176" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="C177" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="C180" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="C181" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="C182" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="C183" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="C184" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="C185" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="C187" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="C188" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="C189" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="C190" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="C194" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="D194" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="E194" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="C195" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="D195" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="C196" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="C197" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="C198" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="C200" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="C201" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="C202" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="C203" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="C204" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="C206" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="C207" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="C208" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="C209" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="C210" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="C211" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="C212" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="C214" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="D214" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="C215" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="C216" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="C217" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="C219" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="C220" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="C221" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="D221" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="E221" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>